--- a/health_coach_forms/002_health_product_satisfaction_survey--health_coach_forms.xlsx
+++ b/health_coach_forms/002_health_product_satisfaction_survey--health_coach_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'4-1',_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '4-1', 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'4-2',_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '4-2', 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'4-3',_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '4-3', 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'4-4',_'name':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '4-4', 'name': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'4-5',_'name':_'terrible'}</t>
+          <t>terrible</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '4-5', 'name': 'Terrible'}</t>
+          <t>Terrible</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'5-1',_'name':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '5-1', 'name': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'5-2',_'name':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '5-2', 'name': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'5-3',_'name':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '5-3', 'name': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'5-4',_'name':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '5-4', 'name': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'5-5',_'name':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '5-5', 'name': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
